--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487693_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487693_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4015</v>
+        <v>4.2946</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8833</v>
+        <v>5.504</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4819</v>
+        <v>-1.2093</v>
       </c>
       <c r="G2" t="n">
         <v>3.1449</v>
@@ -610,13 +610,13 @@
         <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7043</v>
+        <v>0.5975</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.4225</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.09760000000000001</v>
+        <v>0.175</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6119</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9197</v>
+        <v>3.4112</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0255</v>
+        <v>5.6261</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1058</v>
+        <v>-2.2148</v>
       </c>
       <c r="G3" t="n">
         <v>1.3568</v>
@@ -688,13 +688,13 @@
         <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4372</v>
+        <v>0.0544</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4722</v>
+        <v>0.1284</v>
       </c>
       <c r="U3" t="n">
-        <v>0.035</v>
+        <v>-0.074</v>
       </c>
       <c r="V3" t="n">
         <v>1.2239</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9312</v>
+        <v>2.0919</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8772</v>
+        <v>4.0378</v>
       </c>
       <c r="F4" t="n">
         <v>-1.946</v>
@@ -766,10 +766,10 @@
         <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5215</v>
+        <v>0.6822</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2557</v>
+        <v>0.4164</v>
       </c>
       <c r="U4" t="n">
         <v>0.2658</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. JIMÉNEZ BARRETO</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8417</v>
+        <v>1.1269</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1497</v>
+        <v>-1.5542</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.308</v>
+        <v>2.6811</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1203</v>
+        <v>-0.7242</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5948</v>
+        <v>-1.6757</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5254</v>
+        <v>0.9515</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2585</v>
+        <v>-2.5641</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-2.5869</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2585</v>
+        <v>0.0228</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8618</v>
+        <v>1.8399</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5948</v>
+        <v>0.9112</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2669</v>
+        <v>0.9287</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.5821</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0547</v>
+        <v>0.0451</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1088</v>
+        <v>-0.0199</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0541</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2239</v>
+        <v>1.2239</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>A. JIMÉNEZ BARRETO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.8689</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1153</v>
+        <v>1.1497</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8446</v>
+        <v>-0.2808</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7242</v>
+        <v>2.1203</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6757</v>
+        <v>0.5948</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9515</v>
+        <v>1.5254</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.5641</v>
+        <v>1.2585</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.5869</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0228</v>
+        <v>1.2585</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8399</v>
+        <v>0.8618</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9112</v>
+        <v>0.5948</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9287</v>
+        <v>0.2669</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7761</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3524</v>
+        <v>-0.0275</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.581</v>
+        <v>-0.1088</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2286</v>
+        <v>0.0813</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2239</v>
+        <v>-1.2239</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0363</v>
+        <v>-0.0756</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9615</v>
+        <v>1.1222</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9252</v>
+        <v>-1.1978</v>
       </c>
       <c r="G7" t="n">
         <v>0.1003</v>
@@ -1000,13 +1000,13 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0718</v>
+        <v>-0.0401</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.424</v>
+        <v>-0.2633</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4958</v>
+        <v>0.2232</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3299</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9657</v>
+        <v>-2.3218</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7503</v>
+        <v>0.8659</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7846</v>
+        <v>-3.1877</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9568</v>
+        <v>-3.283</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8139999999999999</v>
+        <v>0.8873</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1428</v>
+        <v>-4.1703</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8334</v>
+        <v>0.2224</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2523</v>
+        <v>1.9402</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-1.7178</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1234</v>
+        <v>-3.5054</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4383</v>
+        <v>-1.0529</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5617</v>
+        <v>-2.4525</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1344</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8733</v>
+        <v>1.1552</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9354</v>
+        <v>0.7957</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0621</v>
+        <v>0.3595</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2821</v>
+        <v>1.788</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.161</v>
+        <v>-2.3726</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9449</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1059</v>
+        <v>-1.613</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.283</v>
+        <v>-0.9334</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8873</v>
+        <v>-1.5835</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.1703</v>
+        <v>0.6501</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2224</v>
+        <v>-0.6211</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9402</v>
+        <v>-1.9608</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.7178</v>
+        <v>1.3397</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.5054</v>
+        <v>-0.3123</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0529</v>
+        <v>0.3773</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4525</v>
+        <v>-0.6896</v>
       </c>
       <c r="P9" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.194</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-1.9403</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>1.316</v>
+        <v>-0.1273</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8748</v>
+        <v>0.0555</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4413</v>
+        <v>-0.1828</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
       <c r="W9" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.788</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2814</v>
+        <v>-2.4206</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5594</v>
+        <v>-3.1507</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.722</v>
+        <v>0.7301</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9334</v>
+        <v>-1.9568</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5835</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6501</v>
+        <v>-1.1428</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6211</v>
+        <v>-1.8334</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9608</v>
+        <v>-1.2523</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3397</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3123</v>
+        <v>-0.1234</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3773</v>
+        <v>0.4383</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6896</v>
+        <v>-0.5617</v>
       </c>
       <c r="P10" t="n">
-        <v>0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3881</v>
+        <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0361</v>
+        <v>0.4183</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2557</v>
+        <v>0.535</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2918</v>
+        <v>-0.1166</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.506</v>
+        <v>0.2821</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4865</v>
+        <v>-3.4716</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7334</v>
+        <v>-3.7729</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2469</v>
+        <v>0.3014</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1376</v>
@@ -1312,13 +1312,13 @@
         <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4973</v>
+        <v>0.5123</v>
       </c>
       <c r="T11" t="n">
-        <v>0.268</v>
+        <v>0.2285</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2293</v>
+        <v>0.2838</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8462</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7247</v>
+        <v>-5.2854</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2202</v>
+        <v>-1.9989</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5045</v>
+        <v>-3.2865</v>
       </c>
       <c r="G12" t="n">
         <v>-4.2583</v>
@@ -1390,13 +1390,13 @@
         <v>1.9403</v>
       </c>
       <c r="S12" t="n">
-        <v>0.474</v>
+        <v>0.9132</v>
       </c>
       <c r="T12" t="n">
-        <v>0.572</v>
+        <v>0.7932</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.098</v>
+        <v>0.12</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.759599999999999</v>
+        <v>-4.1541</v>
       </c>
       <c r="E13" t="n">
-        <v>6.463500000000002</v>
+        <v>7.069399999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.2232</v>
+        <v>-11.2233</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.7568</v>
+        <v>-5.756800000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9720000000000004</v>
+        <v>0.9720000000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.729000000000001</v>
+        <v>-6.729</v>
       </c>
       <c r="J13" t="n">
-        <v>5.5728</v>
+        <v>5.572800000000002</v>
       </c>
       <c r="K13" t="n">
         <v>1.3183</v>
@@ -1453,7 +1453,7 @@
         <v>-11.3297</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3459999999999999</v>
+        <v>-0.346</v>
       </c>
       <c r="O13" t="n">
         <v>-10.9837</v>
@@ -1468,13 +1468,13 @@
         <v>10.6719</v>
       </c>
       <c r="S13" t="n">
-        <v>3.577800000000001</v>
+        <v>4.1833</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3775</v>
+        <v>2.9832</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2004</v>
+        <v>1.2003</v>
       </c>
       <c r="V13" t="n">
         <v>0.3299000000000002</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.0718</v>
+        <v>7.7843</v>
       </c>
       <c r="E14" t="n">
-        <v>8.637</v>
+        <v>8.4368</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5652</v>
+        <v>-0.6526</v>
       </c>
       <c r="G14" t="n">
         <v>4.7482</v>
@@ -1546,13 +1546,13 @@
         <v>2.1344</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0902</v>
+        <v>-0.1974</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1233</v>
+        <v>-0.0769</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0331</v>
+        <v>-0.1205</v>
       </c>
       <c r="V14" t="n">
         <v>2.4573</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0523</v>
+        <v>3.9705</v>
       </c>
       <c r="E15" t="n">
         <v>3.834</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2183</v>
+        <v>0.1365</v>
       </c>
       <c r="G15" t="n">
         <v>2.9577</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.1609</v>
       </c>
       <c r="T15" t="n">
         <v>0.0011</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0803</v>
+        <v>-0.162</v>
       </c>
       <c r="V15" t="n">
         <v>0.009599999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5978</v>
+        <v>2.3891</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3758</v>
+        <v>2.1756</v>
       </c>
       <c r="F16" t="n">
-        <v>0.222</v>
+        <v>0.2135</v>
       </c>
       <c r="G16" t="n">
         <v>2.179</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3331</v>
+        <v>0.1245</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0022</v>
+        <v>-0.198</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3309</v>
+        <v>0.3225</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8845</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>D. GONZALEZ  LONGARELA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2953</v>
+        <v>1.1671</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4067</v>
+        <v>1.6871</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1113</v>
+        <v>-0.52</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8844</v>
+        <v>-0.3644</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3394</v>
+        <v>-0.1219</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.545</v>
+        <v>-0.2425</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6673</v>
+        <v>0.3825</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6673</v>
+        <v>0.0577</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.3248</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2171</v>
+        <v>-0.7469</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3279</v>
+        <v>-0.1796</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.545</v>
+        <v>-0.5673</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.3881</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5821</v>
+        <v>1.5523</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6559</v>
+        <v>-0.1968</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8501</v>
+        <v>-0.0954</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1943</v>
+        <v>-0.1015</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9418</v>
+        <v>0.5642</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2239</v>
+        <v>1.788</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1887</v>
+        <v>0.9372</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0875</v>
+        <v>0.8061</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8988</v>
+        <v>0.1311</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3644</v>
+        <v>-0.8844</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1219</v>
+        <v>-0.3394</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2425</v>
+        <v>-0.545</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3825</v>
+        <v>-0.6673</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0577</v>
+        <v>-0.6673</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3248</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7469</v>
+        <v>-0.2171</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1796</v>
+        <v>0.3279</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5673</v>
+        <v>-0.545</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5523</v>
+        <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1752</v>
+        <v>0.2978</v>
       </c>
       <c r="T18" t="n">
-        <v>0.305</v>
+        <v>0.2495</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4802</v>
+        <v>0.0482</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5642</v>
+        <v>0.9418</v>
       </c>
       <c r="W18" t="n">
-        <v>1.788</v>
+        <v>1.2239</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="19">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1939</v>
+        <v>-1.8192</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1342</v>
+        <v>-1.412</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0597</v>
+        <v>-0.4072</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4963</v>
+        <v>-1.3929</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0381</v>
+        <v>-1.057</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4582</v>
+        <v>-0.3359</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8796</v>
+        <v>-1.7309</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2935</v>
+        <v>-1.2893</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5861</v>
+        <v>-0.4415</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3833</v>
+        <v>0.3379</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2554</v>
+        <v>0.2323</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1279</v>
+        <v>0.1056</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.194</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5036</v>
+        <v>-0.2821</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0606</v>
+        <v>-0.2288</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.443</v>
+        <v>-0.0532</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2439</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.6821</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.4382</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3663</v>
+        <v>-1.9242</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3675</v>
+        <v>-2.1342</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9988</v>
+        <v>0.21</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3851</v>
+        <v>-1.4963</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-1.0381</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3029</v>
+        <v>-0.4582</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7268</v>
+        <v>-1.8796</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5437</v>
+        <v>-1.2935</v>
       </c>
       <c r="L22" t="n">
-        <v>3.2706</v>
+        <v>-0.5861</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3417</v>
+        <v>0.3833</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.374</v>
+        <v>0.2554</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9677</v>
+        <v>0.1279</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9403</v>
+        <v>-0.194</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.0747</v>
+        <v>-0.194</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1344</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8789</v>
+        <v>-0.2338</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3017</v>
+        <v>-0.0606</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.1733</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9322</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0477</v>
+        <v>-2.0087</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2128</v>
+        <v>-1.4676</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8349</v>
+        <v>-0.5411</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3929</v>
+        <v>1.3851</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.057</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3359</v>
+        <v>2.3029</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7309</v>
+        <v>2.7268</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2893</v>
+        <v>-0.5437</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4415</v>
+        <v>3.2706</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3379</v>
+        <v>-1.3417</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2323</v>
+        <v>-0.374</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1056</v>
+        <v>-0.9677</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3881</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1344</v>
+        <v>-4.0747</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7463</v>
+        <v>2.1344</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5105</v>
+        <v>-0.5213</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0296</v>
+        <v>-0.4018</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4809</v>
+        <v>-0.1194</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2439</v>
+        <v>-0.9322</v>
       </c>
       <c r="W23" t="n">
-        <v>2.6821</v>
+        <v>0.2821</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4382</v>
+        <v>-1.2143</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5017</v>
+        <v>-3.3978</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4844</v>
+        <v>-0.7837</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0172</v>
+        <v>-2.614</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8443000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>1.7463</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5096</v>
+        <v>-0.4057</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0902</v>
+        <v>-0.3895</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4194</v>
+        <v>-0.0162</v>
       </c>
       <c r="V24" t="n">
         <v>-2.7298</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.759599999999999</v>
+        <v>6.761599999999998</v>
       </c>
       <c r="E25" t="n">
         <v>11.2233</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.4635</v>
+        <v>-4.4617</v>
       </c>
       <c r="G25" t="n">
         <v>5.7569</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9720999999999996</v>
+        <v>-0.9720999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>6.729100000000001</v>
@@ -2380,7 +2380,7 @@
         <v>11.3298</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3462999999999998</v>
+        <v>0.3462999999999994</v>
       </c>
       <c r="L25" t="n">
         <v>10.9837</v>
@@ -2404,13 +2404,13 @@
         <v>13.5824</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.5778</v>
+        <v>-1.5757</v>
       </c>
       <c r="T25" t="n">
         <v>-1.2004</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.3774</v>
+        <v>-0.3754</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3296999999999999</v>
